--- a/Output/PowerPoint_Figures/Fig_3/Fig_3b_Nifedipine_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3b_Nifedipine_data.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,144 +420,144 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>24</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>35</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>40</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>42</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>45</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>48</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>50</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>53</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>55</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>58</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>61</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>63</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>66</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>69</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>71</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>74</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>77</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>79</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>82</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>85</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>87</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>90</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>93</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>8.0.1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.25161562401713</v>
+        <v>39.12580781200852</v>
       </c>
       <c r="C2" t="n">
-        <v>48.93032987005665</v>
+        <v>41.83145616878537</v>
       </c>
       <c r="D2" t="n">
-        <v>49.5986431411323</v>
+        <v>44.69898235584919</v>
       </c>
       <c r="E2" t="n">
-        <v>50.25229648589433</v>
+        <v>47.72075942515742</v>
       </c>
       <c r="F2" t="n">
-        <v>50.88667402861717</v>
+        <v>50.88667402861716</v>
       </c>
       <c r="G2" t="n">
-        <v>51.5034050041163</v>
+        <v>51.50340500411628</v>
       </c>
       <c r="H2" t="n">
-        <v>52.10902561399759</v>
+        <v>52.10902561399757</v>
       </c>
       <c r="I2" t="n">
-        <v>52.71976893316257</v>
+        <v>52.71976893316252</v>
       </c>
       <c r="J2" t="n">
-        <v>53.27527767928692</v>
+        <v>53.27527767928689</v>
       </c>
       <c r="K2" t="n">
-        <v>53.77906224382729</v>
+        <v>53.77906224382731</v>
       </c>
       <c r="L2" t="n">
         <v>54.19596519237295</v>
@@ -578,40 +566,40 @@
         <v>54.50700423425332</v>
       </c>
       <c r="N2" t="n">
-        <v>54.77185595103095</v>
+        <v>54.77185595103096</v>
       </c>
       <c r="O2" t="n">
         <v>55.01820880890995</v>
       </c>
       <c r="P2" t="n">
-        <v>55.25779668238569</v>
+        <v>55.25779668238567</v>
       </c>
       <c r="Q2" t="n">
         <v>55.50450363002786</v>
       </c>
       <c r="R2" t="n">
-        <v>55.76713995200738</v>
+        <v>55.76713995200739</v>
       </c>
       <c r="S2" t="n">
-        <v>56.03691870982093</v>
+        <v>56.03691870982092</v>
       </c>
       <c r="T2" t="n">
-        <v>56.29947012556329</v>
+        <v>56.2994701255633</v>
       </c>
       <c r="U2" t="n">
-        <v>56.55036066193578</v>
+        <v>56.55036066193579</v>
       </c>
       <c r="V2" t="n">
-        <v>56.80154204205521</v>
+        <v>56.80154204205522</v>
       </c>
       <c r="W2" t="n">
-        <v>57.07222238520126</v>
+        <v>57.07222238520129</v>
       </c>
       <c r="X2" t="n">
         <v>57.37535681053251</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.70494378507593</v>
+        <v>57.70494378507594</v>
       </c>
       <c r="Z2" t="n">
         <v>58.04316754119801</v>
@@ -626,95 +614,95 @@
         <v>59.09932823771747</v>
       </c>
       <c r="AD2" t="n">
-        <v>59.46664411121517</v>
+        <v>59.46664411121519</v>
       </c>
       <c r="AE2" t="n">
-        <v>59.83657074084257</v>
+        <v>59.83657074084259</v>
       </c>
       <c r="AF2" t="n">
-        <v>60.20862030532584</v>
+        <v>60.20862030532583</v>
       </c>
       <c r="AG2" t="n">
-        <v>60.58198758767276</v>
+        <v>60.58198758767281</v>
       </c>
       <c r="AH2" t="n">
-        <v>60.95631614405961</v>
+        <v>60.95631614405968</v>
       </c>
       <c r="AI2" t="n">
-        <v>61.3309896348738</v>
+        <v>61.33098963487388</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.68032223585397</v>
+        <v>31.20483072672743</v>
       </c>
       <c r="C3" t="n">
-        <v>35.1521876423384</v>
+        <v>33.02501548239984</v>
       </c>
       <c r="D3" t="n">
-        <v>37.59264556184251</v>
+        <v>35.502806528974</v>
       </c>
       <c r="E3" t="n">
-        <v>39.98787313048185</v>
+        <v>38.61331620210907</v>
       </c>
       <c r="F3" t="n">
-        <v>42.32238847242703</v>
+        <v>42.32238847242708</v>
       </c>
       <c r="G3" t="n">
-        <v>44.60127861444643</v>
+        <v>44.6012786144465</v>
       </c>
       <c r="H3" t="n">
-        <v>46.84971878914565</v>
+        <v>46.84971878914566</v>
       </c>
       <c r="I3" t="n">
-        <v>49.13137712451306</v>
+        <v>49.13137712451309</v>
       </c>
       <c r="J3" t="n">
-        <v>51.24113514473373</v>
+        <v>51.24113514473378</v>
       </c>
       <c r="K3" t="n">
         <v>53.04462582701361</v>
       </c>
       <c r="L3" t="n">
-        <v>54.32526108300153</v>
+        <v>54.32526108300154</v>
       </c>
       <c r="M3" t="n">
         <v>55.00134463325769</v>
       </c>
       <c r="N3" t="n">
-        <v>55.40090763538097</v>
+        <v>55.40090763538096</v>
       </c>
       <c r="O3" t="n">
-        <v>55.65072174037689</v>
+        <v>55.65072174037688</v>
       </c>
       <c r="P3" t="n">
-        <v>55.77968471875551</v>
+        <v>55.77968471875549</v>
       </c>
       <c r="Q3" t="n">
-        <v>55.80362211938178</v>
+        <v>55.80362211938179</v>
       </c>
       <c r="R3" t="n">
         <v>55.73546528837598</v>
       </c>
       <c r="S3" t="n">
-        <v>55.61546572892562</v>
+        <v>55.61546572892563</v>
       </c>
       <c r="T3" t="n">
-        <v>55.48369567247104</v>
+        <v>55.48369567247106</v>
       </c>
       <c r="U3" t="n">
-        <v>55.34433157148085</v>
+        <v>55.34433157148086</v>
       </c>
       <c r="V3" t="n">
-        <v>55.19090239956115</v>
+        <v>55.19090239956117</v>
       </c>
       <c r="W3" t="n">
-        <v>55.03978951912213</v>
+        <v>55.03978951912214</v>
       </c>
       <c r="X3" t="n">
         <v>54.92104538675232</v>
@@ -723,86 +711,86 @@
         <v>54.8581301447461</v>
       </c>
       <c r="Z3" t="n">
-        <v>54.83974764341743</v>
+        <v>54.83974764341744</v>
       </c>
       <c r="AA3" t="n">
-        <v>54.82418420081525</v>
+        <v>54.82418420081527</v>
       </c>
       <c r="AB3" t="n">
         <v>54.78640471536423</v>
       </c>
       <c r="AC3" t="n">
-        <v>54.72935480457381</v>
+        <v>54.72935480457379</v>
       </c>
       <c r="AD3" t="n">
-        <v>54.66667657129288</v>
+        <v>54.66667657129286</v>
       </c>
       <c r="AE3" t="n">
-        <v>54.60815683298894</v>
+        <v>54.60815683298892</v>
       </c>
       <c r="AF3" t="n">
-        <v>54.55682473362138</v>
+        <v>54.5568247336214</v>
       </c>
       <c r="AG3" t="n">
-        <v>54.51180451498711</v>
+        <v>54.51180451498713</v>
       </c>
       <c r="AH3" t="n">
-        <v>54.47070844657718</v>
+        <v>54.47070844657728</v>
       </c>
       <c r="AI3" t="n">
-        <v>54.43186618264952</v>
+        <v>54.43186618264949</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>4.0.2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.10652312139912</v>
+        <v>10.10652312139911</v>
       </c>
       <c r="C4" t="n">
         <v>13.05519578586753</v>
       </c>
       <c r="D4" t="n">
-        <v>16.03588857048066</v>
+        <v>16.03588857048065</v>
       </c>
       <c r="E4" t="n">
-        <v>19.05967114369513</v>
+        <v>19.05967114369515</v>
       </c>
       <c r="F4" t="n">
-        <v>22.13877449408248</v>
+        <v>22.13877449408249</v>
       </c>
       <c r="G4" t="n">
-        <v>25.2763780937595</v>
+        <v>25.27637809375949</v>
       </c>
       <c r="H4" t="n">
-        <v>28.46383598007754</v>
+        <v>28.46383598007753</v>
       </c>
       <c r="I4" t="n">
-        <v>31.68179584074215</v>
+        <v>31.68179584074214</v>
       </c>
       <c r="J4" t="n">
         <v>34.93268015189453</v>
       </c>
       <c r="K4" t="n">
-        <v>37.93585374466882</v>
+        <v>37.93585374466881</v>
       </c>
       <c r="L4" t="n">
-        <v>40.72086580648458</v>
+        <v>40.72086580648459</v>
       </c>
       <c r="M4" t="n">
         <v>43.3399138121593</v>
       </c>
       <c r="N4" t="n">
-        <v>45.71909279346266</v>
+        <v>45.71909279346267</v>
       </c>
       <c r="O4" t="n">
-        <v>47.70402000165674</v>
+        <v>47.70402000165675</v>
       </c>
       <c r="P4" t="n">
-        <v>49.17777633577106</v>
+        <v>49.17777633577104</v>
       </c>
       <c r="Q4" t="n">
         <v>50.15054275186274</v>
@@ -811,13 +799,13 @@
         <v>50.58782898727522</v>
       </c>
       <c r="S4" t="n">
-        <v>50.51849827527165</v>
+        <v>50.51849827527166</v>
       </c>
       <c r="T4" t="n">
-        <v>50.20689597458224</v>
+        <v>50.20689597458222</v>
       </c>
       <c r="U4" t="n">
-        <v>49.82406067944756</v>
+        <v>49.82406067944754</v>
       </c>
       <c r="V4" t="n">
         <v>49.45008059645833</v>
@@ -829,53 +817,53 @@
         <v>48.90945994761282</v>
       </c>
       <c r="Y4" t="n">
-        <v>48.82030567208435</v>
+        <v>48.82030567208434</v>
       </c>
       <c r="Z4" t="n">
-        <v>48.8537477425045</v>
+        <v>48.85374774250452</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.94980853818525</v>
+        <v>48.94980853818527</v>
       </c>
       <c r="AB4" t="n">
-        <v>49.04503165072172</v>
+        <v>49.04503165072171</v>
       </c>
       <c r="AC4" t="n">
-        <v>49.07765712988436</v>
+        <v>49.07765712988437</v>
       </c>
       <c r="AD4" t="n">
-        <v>49.09716056130954</v>
+        <v>49.09716056130953</v>
       </c>
       <c r="AE4" t="n">
-        <v>49.11421512752985</v>
+        <v>49.1142151275298</v>
       </c>
       <c r="AF4" t="n">
-        <v>49.12917258627738</v>
+        <v>49.12917258627745</v>
       </c>
       <c r="AG4" t="n">
-        <v>49.13982792883896</v>
+        <v>49.13982792883898</v>
       </c>
       <c r="AH4" t="n">
-        <v>49.14379886063708</v>
+        <v>49.14379886063727</v>
       </c>
       <c r="AI4" t="n">
-        <v>49.1394881187324</v>
+        <v>49.13948811873243</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>4.0.1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.811628514159905</v>
+        <v>9.811628514159894</v>
       </c>
       <c r="C5" t="n">
-        <v>11.68955804918267</v>
+        <v>11.68955804918263</v>
       </c>
       <c r="D5" t="n">
-        <v>13.57797585799371</v>
+        <v>13.57797585799369</v>
       </c>
       <c r="E5" t="n">
         <v>15.47794991120064</v>
@@ -893,37 +881,37 @@
         <v>23.10031582459911</v>
       </c>
       <c r="J5" t="n">
-        <v>24.92139746660204</v>
+        <v>24.92139746660205</v>
       </c>
       <c r="K5" t="n">
         <v>26.64493930493065</v>
       </c>
       <c r="L5" t="n">
-        <v>28.26437057473505</v>
+        <v>28.26437057473504</v>
       </c>
       <c r="M5" t="n">
         <v>29.74440971708908</v>
       </c>
       <c r="N5" t="n">
-        <v>31.04837410087532</v>
+        <v>31.04837410087533</v>
       </c>
       <c r="O5" t="n">
-        <v>32.16401155239695</v>
+        <v>32.16401155239696</v>
       </c>
       <c r="P5" t="n">
-        <v>33.08294053073292</v>
+        <v>33.08294053073291</v>
       </c>
       <c r="Q5" t="n">
-        <v>33.79541836816095</v>
+        <v>33.79541836816093</v>
       </c>
       <c r="R5" t="n">
-        <v>34.31253542457035</v>
+        <v>34.31253542457033</v>
       </c>
       <c r="S5" t="n">
-        <v>34.67403121166698</v>
+        <v>34.67403121166699</v>
       </c>
       <c r="T5" t="n">
-        <v>34.91467370285287</v>
+        <v>34.91467370285286</v>
       </c>
       <c r="U5" t="n">
         <v>35.05083564257799</v>
@@ -935,65 +923,65 @@
         <v>35.09241139505504</v>
       </c>
       <c r="X5" t="n">
-        <v>35.0438995349356</v>
+        <v>35.04389953493559</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.9751630037546</v>
+        <v>34.97516300375458</v>
       </c>
       <c r="Z5" t="n">
-        <v>34.88488551456507</v>
+        <v>34.88488551456508</v>
       </c>
       <c r="AA5" t="n">
-        <v>34.76338379288893</v>
+        <v>34.76338379288892</v>
       </c>
       <c r="AB5" t="n">
-        <v>34.61337421724699</v>
+        <v>34.613374217247</v>
       </c>
       <c r="AC5" t="n">
-        <v>34.44931422652725</v>
+        <v>34.44931422652724</v>
       </c>
       <c r="AD5" t="n">
-        <v>34.29166144523137</v>
+        <v>34.29166144523138</v>
       </c>
       <c r="AE5" t="n">
-        <v>34.13660271835508</v>
+        <v>34.13660271835507</v>
       </c>
       <c r="AF5" t="n">
         <v>33.981743134341</v>
       </c>
       <c r="AG5" t="n">
-        <v>33.82495019701476</v>
+        <v>33.82495019701467</v>
       </c>
       <c r="AH5" t="n">
-        <v>33.66588422620099</v>
+        <v>33.66588422620112</v>
       </c>
       <c r="AI5" t="n">
-        <v>33.50530404860885</v>
+        <v>33.50530404860883</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2.0.3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.24550970196833</v>
+        <v>19.24550970196837</v>
       </c>
       <c r="C6" t="n">
-        <v>20.89030351135153</v>
+        <v>20.89030351135155</v>
       </c>
       <c r="D6" t="n">
-        <v>22.54951489443231</v>
+        <v>22.54951489443233</v>
       </c>
       <c r="E6" t="n">
-        <v>24.21833180481627</v>
+        <v>24.2183318048163</v>
       </c>
       <c r="F6" t="n">
-        <v>25.88791470219547</v>
+        <v>25.8879147021955</v>
       </c>
       <c r="G6" t="n">
-        <v>27.54529360363982</v>
+        <v>27.54529360363983</v>
       </c>
       <c r="H6" t="n">
         <v>29.17163805771214</v>
@@ -1002,31 +990,31 @@
         <v>30.75633740143511</v>
       </c>
       <c r="J6" t="n">
-        <v>32.36967660094213</v>
+        <v>32.36967660094214</v>
       </c>
       <c r="K6" t="n">
         <v>33.83600372900589</v>
       </c>
       <c r="L6" t="n">
-        <v>35.09169892971893</v>
+        <v>35.09169892971894</v>
       </c>
       <c r="M6" t="n">
         <v>36.18846271378096</v>
       </c>
       <c r="N6" t="n">
-        <v>37.14971988379801</v>
+        <v>37.149719883798</v>
       </c>
       <c r="O6" t="n">
-        <v>37.93817404984704</v>
+        <v>37.93817404984706</v>
       </c>
       <c r="P6" t="n">
-        <v>38.49197014618733</v>
+        <v>38.49197014618735</v>
       </c>
       <c r="Q6" t="n">
         <v>38.85969988771551</v>
       </c>
       <c r="R6" t="n">
-        <v>39.14872634969792</v>
+        <v>39.14872634969791</v>
       </c>
       <c r="S6" t="n">
         <v>39.4149053826309</v>
@@ -1047,16 +1035,16 @@
         <v>40.37025429285365</v>
       </c>
       <c r="Y6" t="n">
-        <v>40.44287379323571</v>
+        <v>40.44287379323572</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.47186136837833</v>
+        <v>40.47186136837834</v>
       </c>
       <c r="AA6" t="n">
         <v>40.4503226190895</v>
       </c>
       <c r="AB6" t="n">
-        <v>40.36419074236581</v>
+        <v>40.36419074236582</v>
       </c>
       <c r="AC6" t="n">
         <v>40.15556372088045</v>
@@ -1071,17 +1059,17 @@
         <v>39.46855540423595</v>
       </c>
       <c r="AG6" t="n">
-        <v>39.23121027915423</v>
+        <v>39.2312102791542</v>
       </c>
       <c r="AH6" t="n">
-        <v>38.98910076463537</v>
+        <v>38.98910076463527</v>
       </c>
       <c r="AI6" t="n">
-        <v>38.7410496948804</v>
+        <v>38.74104969488027</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
@@ -1090,55 +1078,55 @@
         <v>15.12396054298893</v>
       </c>
       <c r="C7" t="n">
-        <v>15.95368289122254</v>
+        <v>15.95368289122255</v>
       </c>
       <c r="D7" t="n">
         <v>16.83220469746517</v>
       </c>
       <c r="E7" t="n">
-        <v>17.76956832750077</v>
+        <v>17.76956832750076</v>
       </c>
       <c r="F7" t="n">
-        <v>18.76613873963064</v>
+        <v>18.76613873963062</v>
       </c>
       <c r="G7" t="n">
         <v>19.81483425576063</v>
       </c>
       <c r="H7" t="n">
-        <v>20.90569450390402</v>
+        <v>20.90569450390401</v>
       </c>
       <c r="I7" t="n">
         <v>22.02603697388487</v>
       </c>
       <c r="J7" t="n">
-        <v>23.52640133249651</v>
+        <v>23.52640133249652</v>
       </c>
       <c r="K7" t="n">
-        <v>25.21124619533282</v>
+        <v>25.21124619533281</v>
       </c>
       <c r="L7" t="n">
-        <v>27.10265881477498</v>
+        <v>27.10265881477497</v>
       </c>
       <c r="M7" t="n">
-        <v>29.16262811216743</v>
+        <v>29.16262811216744</v>
       </c>
       <c r="N7" t="n">
-        <v>31.25739302999927</v>
+        <v>31.25739302999928</v>
       </c>
       <c r="O7" t="n">
-        <v>33.25778327618045</v>
+        <v>33.25778327618044</v>
       </c>
       <c r="P7" t="n">
-        <v>35.08645608078936</v>
+        <v>35.08645608078935</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.69923375794149</v>
+        <v>36.69923375794148</v>
       </c>
       <c r="R7" t="n">
         <v>38.0850402748599</v>
       </c>
       <c r="S7" t="n">
-        <v>39.21475489531615</v>
+        <v>39.21475489531616</v>
       </c>
       <c r="T7" t="n">
         <v>40.05426193947219</v>
@@ -1153,7 +1141,7 @@
         <v>40.74451784623875</v>
       </c>
       <c r="X7" t="n">
-        <v>40.50122363022484</v>
+        <v>40.50122363022483</v>
       </c>
       <c r="Y7" t="n">
         <v>40.16105910911193</v>
@@ -1162,59 +1150,59 @@
         <v>39.80775154545701</v>
       </c>
       <c r="AA7" t="n">
-        <v>39.4931440108731</v>
+        <v>39.49314401087311</v>
       </c>
       <c r="AB7" t="n">
         <v>39.22952132956161</v>
       </c>
       <c r="AC7" t="n">
-        <v>39.1696540476864</v>
+        <v>39.16965404768641</v>
       </c>
       <c r="AD7" t="n">
-        <v>39.11688745445023</v>
+        <v>39.11688745445022</v>
       </c>
       <c r="AE7" t="n">
-        <v>39.06997044966131</v>
+        <v>39.06997044966127</v>
       </c>
       <c r="AF7" t="n">
-        <v>39.03773133441187</v>
+        <v>39.03773133441185</v>
       </c>
       <c r="AG7" t="n">
-        <v>39.02698892805914</v>
+        <v>39.02698892805915</v>
       </c>
       <c r="AH7" t="n">
-        <v>39.04161867739149</v>
+        <v>39.04161867739148</v>
       </c>
       <c r="AI7" t="n">
-        <v>39.08266835793117</v>
+        <v>39.08266835793119</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2.0.1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.62454869063641</v>
+        <v>19.62454869063644</v>
       </c>
       <c r="C8" t="n">
-        <v>20.68835639132819</v>
+        <v>20.68835639132821</v>
       </c>
       <c r="D8" t="n">
-        <v>21.76521132313141</v>
+        <v>21.76521132313138</v>
       </c>
       <c r="E8" t="n">
         <v>22.84912873920562</v>
       </c>
       <c r="F8" t="n">
-        <v>23.9316425802238</v>
+        <v>23.93164258022379</v>
       </c>
       <c r="G8" t="n">
-        <v>25.00585798933824</v>
+        <v>25.00585798933825</v>
       </c>
       <c r="H8" t="n">
-        <v>26.07115255764169</v>
+        <v>26.0711525576417</v>
       </c>
       <c r="I8" t="n">
         <v>27.14568095045571</v>
@@ -1226,7 +1214,7 @@
         <v>29.20222469866285</v>
       </c>
       <c r="L8" t="n">
-        <v>30.10491920117571</v>
+        <v>30.10491920117572</v>
       </c>
       <c r="M8" t="n">
         <v>30.92451597002482</v>
@@ -1235,28 +1223,28 @@
         <v>31.66090436219211</v>
       </c>
       <c r="O8" t="n">
-        <v>32.30610464090988</v>
+        <v>32.30610464090987</v>
       </c>
       <c r="P8" t="n">
-        <v>32.84753805171952</v>
+        <v>32.84753805171951</v>
       </c>
       <c r="Q8" t="n">
         <v>33.2815004450734</v>
       </c>
       <c r="R8" t="n">
-        <v>33.62059926236606</v>
+        <v>33.62059926236608</v>
       </c>
       <c r="S8" t="n">
         <v>33.88696017871136</v>
       </c>
       <c r="T8" t="n">
-        <v>34.09252615777493</v>
+        <v>34.09252615777492</v>
       </c>
       <c r="U8" t="n">
         <v>34.23732636338057</v>
       </c>
       <c r="V8" t="n">
-        <v>34.32858446648555</v>
+        <v>34.32858446648554</v>
       </c>
       <c r="W8" t="n">
         <v>34.3830112921338</v>
@@ -1265,65 +1253,65 @@
         <v>34.40972131988912</v>
       </c>
       <c r="Y8" t="n">
-        <v>34.41068173260308</v>
+        <v>34.41068173260309</v>
       </c>
       <c r="Z8" t="n">
         <v>34.37668575645459</v>
       </c>
       <c r="AA8" t="n">
-        <v>34.30014241270057</v>
+        <v>34.30014241270058</v>
       </c>
       <c r="AB8" t="n">
-        <v>34.18050316179446</v>
+        <v>34.18050316179445</v>
       </c>
       <c r="AC8" t="n">
         <v>33.99844634612295</v>
       </c>
       <c r="AD8" t="n">
-        <v>33.81458750147306</v>
+        <v>33.81458750147307</v>
       </c>
       <c r="AE8" t="n">
-        <v>33.63208734896884</v>
+        <v>33.63208734896882</v>
       </c>
       <c r="AF8" t="n">
-        <v>33.44853126167475</v>
+        <v>33.44853126167477</v>
       </c>
       <c r="AG8" t="n">
-        <v>33.26110543724572</v>
+        <v>33.26110543724575</v>
       </c>
       <c r="AH8" t="n">
-        <v>33.06757662344337</v>
+        <v>33.06757662344339</v>
       </c>
       <c r="AI8" t="n">
-        <v>32.86674743472835</v>
+        <v>32.86674743472834</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2.0.2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.7344075765837</v>
+        <v>27.73440757658368</v>
       </c>
       <c r="C9" t="n">
         <v>26.5408342497959</v>
       </c>
       <c r="D9" t="n">
-        <v>25.38829438593174</v>
+        <v>25.38829438593171</v>
       </c>
       <c r="E9" t="n">
-        <v>24.28479491665642</v>
+        <v>24.28479491665643</v>
       </c>
       <c r="F9" t="n">
-        <v>23.22946378800241</v>
+        <v>23.22946378800242</v>
       </c>
       <c r="G9" t="n">
-        <v>22.21741287027182</v>
+        <v>22.2174128702718</v>
       </c>
       <c r="H9" t="n">
-        <v>21.24263289920221</v>
+        <v>21.2426328992022</v>
       </c>
       <c r="I9" t="n">
         <v>20.30050102263087</v>
@@ -1338,7 +1326,7 @@
         <v>19.22259748609502</v>
       </c>
       <c r="M9" t="n">
-        <v>19.21750745734583</v>
+        <v>19.21750745734582</v>
       </c>
       <c r="N9" t="n">
         <v>19.32055201689595</v>
@@ -1353,7 +1341,7 @@
         <v>19.93750816924859</v>
       </c>
       <c r="R9" t="n">
-        <v>20.16396822334932</v>
+        <v>20.16396822334931</v>
       </c>
       <c r="S9" t="n">
         <v>20.34885147455255</v>
@@ -1362,7 +1350,7 @@
         <v>20.44610666717394</v>
       </c>
       <c r="U9" t="n">
-        <v>20.43846520430606</v>
+        <v>20.43846520430604</v>
       </c>
       <c r="V9" t="n">
         <v>20.35548368848092</v>
@@ -1377,13 +1365,13 @@
         <v>20.23657673530893</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.35652938061401</v>
+        <v>20.356529380614</v>
       </c>
       <c r="AA9" t="n">
         <v>20.54779609701193</v>
       </c>
       <c r="AB9" t="n">
-        <v>20.76763148152886</v>
+        <v>20.76763148152885</v>
       </c>
       <c r="AC9" t="n">
         <v>21.0623734995156</v>
@@ -1395,20 +1383,20 @@
         <v>21.59175957829167</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.88376110343555</v>
+        <v>21.88376110343552</v>
       </c>
       <c r="AG9" t="n">
-        <v>22.19771206298844</v>
+        <v>22.19771206298845</v>
       </c>
       <c r="AH9" t="n">
         <v>22.52674923159951</v>
       </c>
       <c r="AI9" t="n">
-        <v>22.86061931842682</v>
+        <v>22.86061931842689</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1.0.1</t>
         </is>
@@ -1417,40 +1405,40 @@
         <v>8.601917011195345</v>
       </c>
       <c r="C10" t="n">
-        <v>9.709423435939337</v>
+        <v>9.709423435939316</v>
       </c>
       <c r="D10" t="n">
         <v>10.81244865776875</v>
       </c>
       <c r="E10" t="n">
-        <v>11.91095657458121</v>
+        <v>11.9109565745812</v>
       </c>
       <c r="F10" t="n">
-        <v>13.0070820822812</v>
+        <v>13.00708208228121</v>
       </c>
       <c r="G10" t="n">
-        <v>14.10436805597816</v>
+        <v>14.10436805597815</v>
       </c>
       <c r="H10" t="n">
         <v>15.2042212822574</v>
       </c>
       <c r="I10" t="n">
-        <v>16.30516087828976</v>
+        <v>16.30516087828975</v>
       </c>
       <c r="J10" t="n">
-        <v>17.36674973122933</v>
+        <v>17.36674973122934</v>
       </c>
       <c r="K10" t="n">
         <v>18.36437783705752</v>
       </c>
       <c r="L10" t="n">
-        <v>19.28741630940837</v>
+        <v>19.28741630940836</v>
       </c>
       <c r="M10" t="n">
         <v>20.14882543984702</v>
       </c>
       <c r="N10" t="n">
-        <v>20.94913142932755</v>
+        <v>20.94913142932756</v>
       </c>
       <c r="O10" t="n">
         <v>21.67208654972132</v>
@@ -1477,7 +1465,7 @@
         <v>23.95454837090591</v>
       </c>
       <c r="W10" t="n">
-        <v>23.9164059079289</v>
+        <v>23.91640590792891</v>
       </c>
       <c r="X10" t="n">
         <v>23.81352940232362</v>
@@ -1492,10 +1480,10 @@
         <v>23.23940413946314</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.97841579472557</v>
+        <v>22.97841579472556</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.67882070589439</v>
+        <v>22.67882070589438</v>
       </c>
       <c r="AD10" t="n">
         <v>22.36794399278048</v>
@@ -1504,7 +1492,7 @@
         <v>22.05659704237932</v>
       </c>
       <c r="AF10" t="n">
-        <v>21.74759123292299</v>
+        <v>21.747591232923</v>
       </c>
       <c r="AG10" t="n">
         <v>21.44126411759435</v>
@@ -1513,56 +1501,56 @@
         <v>21.13647699496099</v>
       </c>
       <c r="AI10" t="n">
-        <v>20.83179358292593</v>
+        <v>20.83179358292594</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.307395812382958</v>
+        <v>3.307395812383055</v>
       </c>
       <c r="C11" t="n">
-        <v>3.794969197742788</v>
+        <v>3.794969197742878</v>
       </c>
       <c r="D11" t="n">
-        <v>4.28297577365887</v>
+        <v>4.282975773658886</v>
       </c>
       <c r="E11" t="n">
-        <v>4.771611535520587</v>
+        <v>4.77161153552054</v>
       </c>
       <c r="F11" t="n">
-        <v>5.261199724315286</v>
+        <v>5.261199724315248</v>
       </c>
       <c r="G11" t="n">
-        <v>5.752302461826925</v>
+        <v>5.752302461826969</v>
       </c>
       <c r="H11" t="n">
-        <v>6.245958394406759</v>
+        <v>6.245958394406764</v>
       </c>
       <c r="I11" t="n">
-        <v>6.744217127893564</v>
+        <v>6.744217127893551</v>
       </c>
       <c r="J11" t="n">
-        <v>7.154760132475577</v>
+        <v>7.154760132475582</v>
       </c>
       <c r="K11" t="n">
         <v>7.730693680365945</v>
       </c>
       <c r="L11" t="n">
-        <v>8.384497082020751</v>
+        <v>8.384497082020756</v>
       </c>
       <c r="M11" t="n">
-        <v>9.055474284634196</v>
+        <v>9.055474284634192</v>
       </c>
       <c r="N11" t="n">
-        <v>9.719294317856951</v>
+        <v>9.719294317856949</v>
       </c>
       <c r="O11" t="n">
-        <v>10.36005894429939</v>
+        <v>10.3600589442994</v>
       </c>
       <c r="P11" t="n">
         <v>10.97318093972</v>
@@ -1589,10 +1577,10 @@
         <v>13.11270456107522</v>
       </c>
       <c r="X11" t="n">
-        <v>13.01414295979314</v>
+        <v>13.01414295979313</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.8516836833131</v>
+        <v>12.85168368331311</v>
       </c>
       <c r="Z11" t="n">
         <v>12.64681653899561</v>
@@ -1616,53 +1604,53 @@
         <v>11.15003991958065</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.90521318705315</v>
+        <v>10.90521318705314</v>
       </c>
       <c r="AH11" t="n">
-        <v>10.66340522752906</v>
+        <v>10.66340522752908</v>
       </c>
       <c r="AI11" t="n">
-        <v>10.42522933944565</v>
+        <v>10.42522933944564</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>1.0.2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.182063169304998</v>
+        <v>3.182063169304994</v>
       </c>
       <c r="C12" t="n">
-        <v>4.008798041461633</v>
+        <v>4.00879804146163</v>
       </c>
       <c r="D12" t="n">
-        <v>4.844229339124083</v>
+        <v>4.844229339124079</v>
       </c>
       <c r="E12" t="n">
-        <v>5.679591312450579</v>
+        <v>5.679591312450571</v>
       </c>
       <c r="F12" t="n">
-        <v>6.505922400713572</v>
+        <v>6.50592240071357</v>
       </c>
       <c r="G12" t="n">
-        <v>7.318139510505878</v>
+        <v>7.318139510505874</v>
       </c>
       <c r="H12" t="n">
-        <v>8.117617763245647</v>
+        <v>8.117617763245642</v>
       </c>
       <c r="I12" t="n">
-        <v>8.921637870081307</v>
+        <v>8.921637870081303</v>
       </c>
       <c r="J12" t="n">
-        <v>9.660003997813986</v>
+        <v>9.660003997813979</v>
       </c>
       <c r="K12" t="n">
         <v>10.35737566583646</v>
       </c>
       <c r="L12" t="n">
-        <v>10.99054429693441</v>
+        <v>10.9905442969344</v>
       </c>
       <c r="M12" t="n">
         <v>11.53133424068364</v>
@@ -1674,7 +1662,7 @@
         <v>12.26545950079867</v>
       </c>
       <c r="P12" t="n">
-        <v>12.44270670850675</v>
+        <v>12.44270670850674</v>
       </c>
       <c r="Q12" t="n">
         <v>12.51687351480416</v>
@@ -1704,13 +1692,13 @@
         <v>12.07753520538872</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.04006244793113</v>
+        <v>12.04006244793114</v>
       </c>
       <c r="AA12" t="n">
         <v>12.04136173728072</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.06103939141702</v>
+        <v>12.06103939141701</v>
       </c>
       <c r="AC12" t="n">
         <v>11.98967361919662</v>
@@ -1725,23 +1713,23 @@
         <v>11.71983853378149</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.61543543399198</v>
+        <v>11.61543543399196</v>
       </c>
       <c r="AH12" t="n">
-        <v>11.49962902841657</v>
+        <v>11.49962902841655</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.37180426483715</v>
+        <v>11.37180426483714</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.5.1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.70820961268417</v>
+        <v>10.70820961268421</v>
       </c>
       <c r="C13" t="n">
         <v>11.79624432575805</v>
@@ -1750,19 +1738,19 @@
         <v>12.8910410369235</v>
       </c>
       <c r="E13" t="n">
-        <v>13.99346208977275</v>
+        <v>13.99346208977276</v>
       </c>
       <c r="F13" t="n">
         <v>15.10659674069614</v>
       </c>
       <c r="G13" t="n">
-        <v>16.23247731704673</v>
+        <v>16.23247731704674</v>
       </c>
       <c r="H13" t="n">
         <v>17.36985460902716</v>
       </c>
       <c r="I13" t="n">
-        <v>18.51618632565101</v>
+        <v>18.516186325651</v>
       </c>
       <c r="J13" t="n">
         <v>19.73309008084469</v>
@@ -1771,7 +1759,7 @@
         <v>20.97132880893755</v>
       </c>
       <c r="L13" t="n">
-        <v>22.19205331922824</v>
+        <v>22.19205331922823</v>
       </c>
       <c r="M13" t="n">
         <v>23.34023408255874</v>
@@ -1780,7 +1768,7 @@
         <v>24.38932854672661</v>
       </c>
       <c r="O13" t="n">
-        <v>25.33631733864877</v>
+        <v>25.33631733864876</v>
       </c>
       <c r="P13" t="n">
         <v>26.19337091738444</v>
@@ -1789,22 +1777,22 @@
         <v>26.94384669785994</v>
       </c>
       <c r="R13" t="n">
-        <v>27.55138424887368</v>
+        <v>27.55138424887369</v>
       </c>
       <c r="S13" t="n">
         <v>27.99753820035335</v>
       </c>
       <c r="T13" t="n">
-        <v>28.26765489129124</v>
+        <v>28.26765489129123</v>
       </c>
       <c r="U13" t="n">
-        <v>28.36328676951219</v>
+        <v>28.3632867695122</v>
       </c>
       <c r="V13" t="n">
         <v>28.31019732168473</v>
       </c>
       <c r="W13" t="n">
-        <v>28.15753525718318</v>
+        <v>28.15753525718321</v>
       </c>
       <c r="X13" t="n">
         <v>27.93500935265438</v>
@@ -1816,7 +1804,7 @@
         <v>27.28863307652373</v>
       </c>
       <c r="AA13" t="n">
-        <v>26.85718056169304</v>
+        <v>26.85718056169305</v>
       </c>
       <c r="AB13" t="n">
         <v>26.36503446082966</v>
@@ -1825,7 +1813,7 @@
         <v>25.79820087290654</v>
       </c>
       <c r="AD13" t="n">
-        <v>25.22715895869835</v>
+        <v>25.22715895869836</v>
       </c>
       <c r="AE13" t="n">
         <v>24.6550581720493</v>
@@ -1837,41 +1825,41 @@
         <v>23.50239797809839</v>
       </c>
       <c r="AH13" t="n">
-        <v>22.91890589190024</v>
+        <v>22.91890589190027</v>
       </c>
       <c r="AI13" t="n">
-        <v>22.3290203382739</v>
+        <v>22.32902033827394</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.206128729298625</v>
+        <v>6.206128729298616</v>
       </c>
       <c r="C14" t="n">
-        <v>6.627045924987459</v>
+        <v>6.627045924987462</v>
       </c>
       <c r="D14" t="n">
-        <v>7.089072687105232</v>
+        <v>7.089072687105233</v>
       </c>
       <c r="E14" t="n">
-        <v>7.585666687369522</v>
+        <v>7.585666687369521</v>
       </c>
       <c r="F14" t="n">
-        <v>8.110457701599335</v>
+        <v>8.110457701599339</v>
       </c>
       <c r="G14" t="n">
-        <v>8.661687307625449</v>
+        <v>8.661687307625447</v>
       </c>
       <c r="H14" t="n">
-        <v>9.247916639408135</v>
+        <v>9.247916639408137</v>
       </c>
       <c r="I14" t="n">
-        <v>9.906664740512056</v>
+        <v>9.906664740512054</v>
       </c>
       <c r="J14" t="n">
         <v>11.05751109087588</v>
@@ -1883,7 +1871,7 @@
         <v>14.08076334589287</v>
       </c>
       <c r="M14" t="n">
-        <v>15.88705996681796</v>
+        <v>15.88705996681797</v>
       </c>
       <c r="N14" t="n">
         <v>17.69831907764069</v>
@@ -1892,10 +1880,10 @@
         <v>19.02192490725961</v>
       </c>
       <c r="P14" t="n">
-        <v>19.60670504024226</v>
+        <v>19.60670504024227</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.7675508136776</v>
+        <v>19.76755081367761</v>
       </c>
       <c r="R14" t="n">
         <v>19.71727230065759</v>
@@ -1904,7 +1892,7 @@
         <v>19.45743890720846</v>
       </c>
       <c r="T14" t="n">
-        <v>18.95194053977054</v>
+        <v>18.95194053977053</v>
       </c>
       <c r="U14" t="n">
         <v>18.13675085614522</v>
@@ -1913,174 +1901,174 @@
         <v>16.71223307455537</v>
       </c>
       <c r="W14" t="n">
-        <v>14.52516154795939</v>
+        <v>14.5251615479594</v>
       </c>
       <c r="X14" t="n">
-        <v>12.13268153594498</v>
+        <v>12.13268153594497</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.975242057501442</v>
+        <v>9.975242057501433</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.141037353173392</v>
+        <v>8.141037353173385</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.628378492143418</v>
+        <v>6.628378492143416</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.440218152757325</v>
+        <v>5.440218152757321</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.965522127769675</v>
+        <v>4.965522127769673</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.541992254780849</v>
+        <v>4.541992254780848</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.159281639152844</v>
+        <v>4.159281639152843</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.821337479226846</v>
+        <v>3.821337479226845</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.53119716567775</v>
+        <v>3.531197165677748</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.29141005673443</v>
+        <v>3.29141005673444</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.102190026419371</v>
+        <v>3.102190026419374</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.5.2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.650442521700589</v>
+        <v>7.650442521700604</v>
       </c>
       <c r="C15" t="n">
-        <v>7.265308533877596</v>
+        <v>7.265308533877601</v>
       </c>
       <c r="D15" t="n">
-        <v>6.909769283572502</v>
+        <v>6.909769283572513</v>
       </c>
       <c r="E15" t="n">
-        <v>6.580977601302529</v>
+        <v>6.580977601302528</v>
       </c>
       <c r="F15" t="n">
-        <v>6.266217144726657</v>
+        <v>6.266217144726669</v>
       </c>
       <c r="G15" t="n">
-        <v>5.938671551374234</v>
+        <v>5.938671551374243</v>
       </c>
       <c r="H15" t="n">
-        <v>5.539935723811295</v>
+        <v>5.539935723811307</v>
       </c>
       <c r="I15" t="n">
-        <v>4.98200628559631</v>
+        <v>4.982006285596321</v>
       </c>
       <c r="J15" t="n">
-        <v>4.980350637382557</v>
+        <v>4.980350637382551</v>
       </c>
       <c r="K15" t="n">
-        <v>5.245197446427531</v>
+        <v>5.245197446427534</v>
       </c>
       <c r="L15" t="n">
-        <v>5.487826989551713</v>
+        <v>5.487826989551714</v>
       </c>
       <c r="M15" t="n">
         <v>5.651762505194959</v>
       </c>
       <c r="N15" t="n">
-        <v>5.735231183080805</v>
+        <v>5.735231183080807</v>
       </c>
       <c r="O15" t="n">
-        <v>5.746315200935629</v>
+        <v>5.74631520093563</v>
       </c>
       <c r="P15" t="n">
         <v>5.699853614055105</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.594241014483741</v>
+        <v>5.59424101448374</v>
       </c>
       <c r="R15" t="n">
-        <v>5.420773672093103</v>
+        <v>5.420773672093107</v>
       </c>
       <c r="S15" t="n">
-        <v>5.198426738921119</v>
+        <v>5.198426738921118</v>
       </c>
       <c r="T15" t="n">
-        <v>4.954960678250171</v>
+        <v>4.95496067825017</v>
       </c>
       <c r="U15" t="n">
-        <v>4.69499930401733</v>
+        <v>4.694999304017328</v>
       </c>
       <c r="V15" t="n">
-        <v>4.416907960814606</v>
+        <v>4.416907960814605</v>
       </c>
       <c r="W15" t="n">
         <v>4.124492836151219</v>
       </c>
       <c r="X15" t="n">
-        <v>3.837558020113681</v>
+        <v>3.837558020113682</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.574774733375803</v>
+        <v>3.574774733375805</v>
       </c>
       <c r="Z15" t="n">
         <v>3.340786365595233</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.137198128403711</v>
+        <v>3.13719812840371</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.95803724353315</v>
+        <v>2.958037243533151</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.806711024899086</v>
+        <v>2.806711024899085</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.653921878917133</v>
+        <v>2.653921878917132</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.50250882293945</v>
+        <v>2.502508822939449</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.353464362169754</v>
+        <v>2.353464362169755</v>
       </c>
       <c r="AG15" t="n">
         <v>2.206447188356084</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.060965463949757</v>
+        <v>2.060965463949752</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.916674968838547</v>
+        <v>1.916674968838556</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.25.1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.9660108542926</v>
+        <v>14.96601085429257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.68597800559426</v>
+        <v>15.68597800559427</v>
       </c>
       <c r="D16" t="n">
-        <v>16.3984529664096</v>
+        <v>16.39845296640959</v>
       </c>
       <c r="E16" t="n">
-        <v>17.10114787515025</v>
+        <v>17.10114787515024</v>
       </c>
       <c r="F16" t="n">
-        <v>17.79192479444269</v>
+        <v>17.7919247944427</v>
       </c>
       <c r="G16" t="n">
         <v>18.46971450759156</v>
@@ -2089,7 +2077,7 @@
         <v>19.13865086689576</v>
       </c>
       <c r="I16" t="n">
-        <v>19.80724401565145</v>
+        <v>19.80724401565144</v>
       </c>
       <c r="J16" t="n">
         <v>20.36251862808185</v>
@@ -2104,10 +2092,10 @@
         <v>21.43148073227654</v>
       </c>
       <c r="N16" t="n">
-        <v>21.59461776618963</v>
+        <v>21.59461776618964</v>
       </c>
       <c r="O16" t="n">
-        <v>21.65411131414575</v>
+        <v>21.65411131414574</v>
       </c>
       <c r="P16" t="n">
         <v>21.62795452541041</v>
@@ -2116,13 +2104,13 @@
         <v>21.52699435587761</v>
       </c>
       <c r="R16" t="n">
-        <v>21.35342657246651</v>
+        <v>21.35342657246652</v>
       </c>
       <c r="S16" t="n">
-        <v>21.10766194884911</v>
+        <v>21.10766194884912</v>
       </c>
       <c r="T16" t="n">
-        <v>20.79348951555551</v>
+        <v>20.79348951555552</v>
       </c>
       <c r="U16" t="n">
         <v>20.41741471638272</v>
@@ -2134,13 +2122,13 @@
         <v>19.49785145981057</v>
       </c>
       <c r="X16" t="n">
-        <v>18.95243103566272</v>
+        <v>18.95243103566273</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.36262989175382</v>
+        <v>18.36262989175383</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.74275696892028</v>
+        <v>17.74275696892027</v>
       </c>
       <c r="AA16" t="n">
         <v>17.10955687889772</v>
@@ -2152,47 +2140,47 @@
         <v>15.84491103104659</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.21294552863382</v>
+        <v>15.21294552863383</v>
       </c>
       <c r="AE16" t="n">
-        <v>14.57927112136867</v>
+        <v>14.57927112136866</v>
       </c>
       <c r="AF16" t="n">
         <v>13.94653367537255</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.31599846916847</v>
+        <v>13.3159984691685</v>
       </c>
       <c r="AH16" t="n">
-        <v>12.68792982101179</v>
+        <v>12.68792982101181</v>
       </c>
       <c r="AI16" t="n">
-        <v>12.06225777098529</v>
+        <v>12.06225777098527</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10.45309970050592</v>
+        <v>10.45309970050591</v>
       </c>
       <c r="C17" t="n">
-        <v>10.51144400372068</v>
+        <v>10.51144400372069</v>
       </c>
       <c r="D17" t="n">
-        <v>10.56727984100539</v>
+        <v>10.5672798410054</v>
       </c>
       <c r="E17" t="n">
-        <v>10.62001674841507</v>
+        <v>10.62001674841508</v>
       </c>
       <c r="F17" t="n">
         <v>10.66939580446264</v>
       </c>
       <c r="G17" t="n">
-        <v>10.71607594264814</v>
+        <v>10.71607594264813</v>
       </c>
       <c r="H17" t="n">
         <v>10.7612246527424</v>
@@ -2204,7 +2192,7 @@
         <v>10.83508640211264</v>
       </c>
       <c r="K17" t="n">
-        <v>10.8638373688056</v>
+        <v>10.86383736880561</v>
       </c>
       <c r="L17" t="n">
         <v>10.89143079587098</v>
@@ -2234,10 +2222,10 @@
         <v>11.51775057231747</v>
       </c>
       <c r="U17" t="n">
-        <v>11.64820894249371</v>
+        <v>11.6482089424937</v>
       </c>
       <c r="V17" t="n">
-        <v>11.77012847362919</v>
+        <v>11.7701284736292</v>
       </c>
       <c r="W17" t="n">
         <v>11.88692658851808</v>
@@ -2249,7 +2237,7 @@
         <v>12.10477645414712</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.17977545306563</v>
+        <v>12.17977545306564</v>
       </c>
       <c r="AA17" t="n">
         <v>12.22299739631495</v>
@@ -2264,68 +2252,68 @@
         <v>12.08326145241223</v>
       </c>
       <c r="AE17" t="n">
-        <v>12.01243091208327</v>
+        <v>12.01243091208328</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.93800478813728</v>
+        <v>11.93800478813729</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.8586672602305</v>
+        <v>11.85866726023052</v>
       </c>
       <c r="AH17" t="n">
-        <v>11.77404661024017</v>
+        <v>11.77404661024018</v>
       </c>
       <c r="AI17" t="n">
-        <v>11.68496448710104</v>
+        <v>11.68496448710107</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.125.1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.028001077949034</v>
+        <v>4.02800107794898</v>
       </c>
       <c r="C18" t="n">
-        <v>5.323958766929388</v>
+        <v>5.323958766929375</v>
       </c>
       <c r="D18" t="n">
-        <v>6.62266357918725</v>
+        <v>6.62266357918723</v>
       </c>
       <c r="E18" t="n">
-        <v>7.924597917961638</v>
+        <v>7.924597917961608</v>
       </c>
       <c r="F18" t="n">
-        <v>9.2302833060987</v>
+        <v>9.230283306098698</v>
       </c>
       <c r="G18" t="n">
-        <v>10.54016171199747</v>
+        <v>10.54016171199744</v>
       </c>
       <c r="H18" t="n">
-        <v>11.85383027274474</v>
+        <v>11.85383027274472</v>
       </c>
       <c r="I18" t="n">
         <v>13.16772130025412</v>
       </c>
       <c r="J18" t="n">
-        <v>14.48106107184288</v>
+        <v>14.48106107184287</v>
       </c>
       <c r="K18" t="n">
         <v>15.79148820319013</v>
       </c>
       <c r="L18" t="n">
-        <v>17.09208211274038</v>
+        <v>17.09208211274039</v>
       </c>
       <c r="M18" t="n">
-        <v>18.37456763958266</v>
+        <v>18.37456763958265</v>
       </c>
       <c r="N18" t="n">
         <v>19.61712612713472</v>
       </c>
       <c r="O18" t="n">
-        <v>20.80190856894857</v>
+        <v>20.80190856894858</v>
       </c>
       <c r="P18" t="n">
         <v>21.91670819042579</v>
@@ -2334,13 +2322,13 @@
         <v>22.92985061858056</v>
       </c>
       <c r="R18" t="n">
-        <v>23.80296355564368</v>
+        <v>23.80296355564369</v>
       </c>
       <c r="S18" t="n">
         <v>24.52360307548746</v>
       </c>
       <c r="T18" t="n">
-        <v>25.10219066104109</v>
+        <v>25.1021906610411</v>
       </c>
       <c r="U18" t="n">
         <v>25.54170357378727</v>
@@ -2349,13 +2337,13 @@
         <v>25.84877442305699</v>
       </c>
       <c r="W18" t="n">
-        <v>26.03146716538933</v>
+        <v>26.03146716538934</v>
       </c>
       <c r="X18" t="n">
         <v>26.09199341668766</v>
       </c>
       <c r="Y18" t="n">
-        <v>26.02768830776493</v>
+        <v>26.02768830776494</v>
       </c>
       <c r="Z18" t="n">
         <v>25.85087221929535</v>
@@ -2367,29 +2355,29 @@
         <v>25.28378512962244</v>
       </c>
       <c r="AC18" t="n">
-        <v>24.97249111498106</v>
+        <v>24.97249111498105</v>
       </c>
       <c r="AD18" t="n">
         <v>24.66370695881399</v>
       </c>
       <c r="AE18" t="n">
-        <v>24.35398095551196</v>
+        <v>24.35398095551195</v>
       </c>
       <c r="AF18" t="n">
-        <v>24.04405632160784</v>
+        <v>24.04405632160787</v>
       </c>
       <c r="AG18" t="n">
-        <v>23.73566767579275</v>
+        <v>23.73566767579279</v>
       </c>
       <c r="AH18" t="n">
-        <v>23.43070492008963</v>
+        <v>23.43070492008967</v>
       </c>
       <c r="AI18" t="n">
-        <v>23.13025138783819</v>
+        <v>23.13025138783821</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>0.125</t>
         </is>
@@ -2398,13 +2386,13 @@
         <v>6.262678104466471</v>
       </c>
       <c r="C19" t="n">
-        <v>6.653916733333528</v>
+        <v>6.653916733333532</v>
       </c>
       <c r="D19" t="n">
-        <v>7.0372905483101</v>
+        <v>7.037290548310102</v>
       </c>
       <c r="E19" t="n">
-        <v>7.409339439020691</v>
+        <v>7.409339439020694</v>
       </c>
       <c r="F19" t="n">
         <v>7.768321649208177</v>
@@ -2416,22 +2404,22 @@
         <v>8.452217715797422</v>
       </c>
       <c r="I19" t="n">
-        <v>8.794998843059345</v>
+        <v>8.794998843059343</v>
       </c>
       <c r="J19" t="n">
-        <v>9.016986141274705</v>
+        <v>9.016986141274707</v>
       </c>
       <c r="K19" t="n">
-        <v>9.205268733474586</v>
+        <v>9.205268733474584</v>
       </c>
       <c r="L19" t="n">
-        <v>9.335142344840492</v>
+        <v>9.33514234484049</v>
       </c>
       <c r="M19" t="n">
-        <v>9.372239631328615</v>
+        <v>9.372239631328618</v>
       </c>
       <c r="N19" t="n">
-        <v>9.329525864545349</v>
+        <v>9.329525864545351</v>
       </c>
       <c r="O19" t="n">
         <v>9.247949706488827</v>
@@ -2440,13 +2428,13 @@
         <v>9.134053198866274</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.996028255709746</v>
+        <v>8.996028255709744</v>
       </c>
       <c r="R19" t="n">
-        <v>8.851232157556453</v>
+        <v>8.851232157556455</v>
       </c>
       <c r="S19" t="n">
-        <v>8.7075708981977</v>
+        <v>8.707570898197705</v>
       </c>
       <c r="T19" t="n">
         <v>8.564705488780332</v>
@@ -2455,25 +2443,25 @@
         <v>8.421051271718751</v>
       </c>
       <c r="V19" t="n">
-        <v>8.280585991660107</v>
+        <v>8.280585991660105</v>
       </c>
       <c r="W19" t="n">
         <v>8.141915111064327</v>
       </c>
       <c r="X19" t="n">
-        <v>8.002546075609095</v>
+        <v>8.002546075609096</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.863666357203699</v>
+        <v>7.863666357203698</v>
       </c>
       <c r="Z19" t="n">
         <v>7.716226508814794</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.547864217682244</v>
+        <v>7.547864217682247</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.353583106323449</v>
+        <v>7.353583106323447</v>
       </c>
       <c r="AC19" t="n">
         <v>7.103774472406728</v>
@@ -2482,23 +2470,23 @@
         <v>6.858685834119854</v>
       </c>
       <c r="AE19" t="n">
-        <v>6.612861581557092</v>
+        <v>6.612861581557087</v>
       </c>
       <c r="AF19" t="n">
-        <v>6.362568310676894</v>
+        <v>6.362568310676897</v>
       </c>
       <c r="AG19" t="n">
-        <v>6.105907659683593</v>
+        <v>6.10590765968359</v>
       </c>
       <c r="AH19" t="n">
-        <v>5.842467383292989</v>
+        <v>5.842467383292984</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.572909921280921</v>
+        <v>5.572909921280915</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>0.0623.1</t>
         </is>
@@ -2507,13 +2495,13 @@
         <v>7.326534524017275</v>
       </c>
       <c r="C20" t="n">
-        <v>7.627660052304703</v>
+        <v>7.627660052304706</v>
       </c>
       <c r="D20" t="n">
-        <v>7.994605128301295</v>
+        <v>7.994605128301293</v>
       </c>
       <c r="E20" t="n">
-        <v>8.4154806985034</v>
+        <v>8.415480698503398</v>
       </c>
       <c r="F20" t="n">
         <v>8.877740906911846</v>
@@ -2561,7 +2549,7 @@
         <v>22.12408976547129</v>
       </c>
       <c r="U20" t="n">
-        <v>21.77396693158955</v>
+        <v>21.77396693158956</v>
       </c>
       <c r="V20" t="n">
         <v>21.31316022695895</v>
@@ -2573,7 +2561,7 @@
         <v>20.70963631317502</v>
       </c>
       <c r="Y20" t="n">
-        <v>20.81469165408243</v>
+        <v>20.81469165408242</v>
       </c>
       <c r="Z20" t="n">
         <v>21.21692326036356</v>
@@ -2591,23 +2579,23 @@
         <v>24.53592841681856</v>
       </c>
       <c r="AE20" t="n">
-        <v>25.47665117661246</v>
+        <v>25.47665117661249</v>
       </c>
       <c r="AF20" t="n">
-        <v>26.43459997323934</v>
+        <v>26.43459997323935</v>
       </c>
       <c r="AG20" t="n">
-        <v>27.39429195384596</v>
+        <v>27.39429195384599</v>
       </c>
       <c r="AH20" t="n">
-        <v>28.33999553186699</v>
+        <v>28.33999553186698</v>
       </c>
       <c r="AI20" t="n">
-        <v>29.25834539578839</v>
+        <v>29.25834539578842</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>0.0623</t>
         </is>
@@ -2622,7 +2610,7 @@
         <v>13.45748981498933</v>
       </c>
       <c r="E21" t="n">
-        <v>13.67058445722257</v>
+        <v>13.67058445722256</v>
       </c>
       <c r="F21" t="n">
         <v>13.88525193682195</v>
@@ -2631,7 +2619,7 @@
         <v>14.0992291482129</v>
       </c>
       <c r="H21" t="n">
-        <v>14.31470409787279</v>
+        <v>14.31470409787278</v>
       </c>
       <c r="I21" t="n">
         <v>14.55050284864884</v>
@@ -2661,10 +2649,10 @@
         <v>17.2870415819353</v>
       </c>
       <c r="R21" t="n">
-        <v>17.52091853405487</v>
+        <v>17.52091853405486</v>
       </c>
       <c r="S21" t="n">
-        <v>17.68804047915804</v>
+        <v>17.68804047915805</v>
       </c>
       <c r="T21" t="n">
         <v>17.80952328884019</v>
@@ -2673,10 +2661,10 @@
         <v>17.91325645803016</v>
       </c>
       <c r="V21" t="n">
-        <v>18.00120825575513</v>
+        <v>18.00120825575514</v>
       </c>
       <c r="W21" t="n">
-        <v>18.09028388804032</v>
+        <v>18.09028388804033</v>
       </c>
       <c r="X21" t="n">
         <v>18.1991893090171</v>
@@ -2685,7 +2673,7 @@
         <v>18.34619931274588</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.53700693077593</v>
+        <v>18.53700693077594</v>
       </c>
       <c r="AA21" t="n">
         <v>18.77121473894945</v>
@@ -2697,22 +2685,22 @@
         <v>19.44885505201019</v>
       </c>
       <c r="AD21" t="n">
-        <v>19.84555668336738</v>
+        <v>19.84555668336739</v>
       </c>
       <c r="AE21" t="n">
-        <v>20.24866436245374</v>
+        <v>20.24866436245376</v>
       </c>
       <c r="AF21" t="n">
-        <v>20.65789668120244</v>
+        <v>20.65789668120241</v>
       </c>
       <c r="AG21" t="n">
-        <v>21.07223479243224</v>
+        <v>21.07223479243223</v>
       </c>
       <c r="AH21" t="n">
-        <v>21.49000790223066</v>
+        <v>21.49000790223069</v>
       </c>
       <c r="AI21" t="n">
-        <v>21.91126029729431</v>
+        <v>21.91126029729432</v>
       </c>
     </row>
   </sheetData>
@@ -2730,509 +2718,509 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_0.00</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_0.97</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_1.94</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>t_2.91</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_3.88</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>t_4.85</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>t_5.82</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>t_6.79</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>t_7.76</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>t_8.73</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>t_9.70</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>t_10.67</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>t_11.64</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>t_12.61</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>t_13.58</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>t_14.55</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>t_15.52</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>t_16.48</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>t_17.45</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>t_18.42</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>t_19.39</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>t_20.36</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>t_21.33</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>t_22.30</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>t_23.27</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>t_24.24</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>t_25.21</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>t_26.18</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>t_27.15</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>t_28.12</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>t_29.09</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>t_30.06</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>t_31.03</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>t_32.00</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>t_32.97</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>t_33.94</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>t_34.91</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>t_35.88</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>t_36.85</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>t_37.82</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>t_38.79</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>t_39.76</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>t_40.73</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>t_41.70</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>t_42.67</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>t_43.64</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>t_44.61</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>t_45.58</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>t_46.55</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>t_47.52</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>t_48.48</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>t_49.45</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>t_50.42</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>t_51.39</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>t_52.36</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>t_53.33</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>t_54.30</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>t_55.27</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>t_56.24</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>t_57.21</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>t_58.18</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>t_59.15</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>t_60.12</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>t_61.09</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>t_62.06</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>t_63.03</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>t_64.00</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>t_64.97</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>t_65.94</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>t_66.91</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>t_67.88</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>t_68.85</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>t_69.82</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>t_70.79</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>t_71.76</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>t_72.73</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>t_73.70</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>t_74.67</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>t_75.64</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>t_76.61</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>t_77.58</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>t_78.55</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>t_79.52</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>t_80.48</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>t_81.45</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>t_82.42</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>t_83.39</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>t_84.36</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>t_85.33</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>t_86.30</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>t_87.27</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>t_88.24</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>t_89.21</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>t_90.18</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>t_91.15</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>t_92.12</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>t_93.09</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>t_94.06</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>t_95.03</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>t_96.00</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>dr_0.0000</t>
         </is>
@@ -3539,7 +3527,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>dr_0.0202</t>
         </is>
@@ -3824,10 +3812,10 @@
         <v>19.41675832331744</v>
       </c>
       <c r="CQ3" t="n">
-        <v>19.41675832455693</v>
+        <v>19.41675832455692</v>
       </c>
       <c r="CR3" t="n">
-        <v>19.41675832578977</v>
+        <v>19.41675832578976</v>
       </c>
       <c r="CS3" t="n">
         <v>19.41675832701607</v>
@@ -3846,7 +3834,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>dr_0.0404</t>
         </is>
@@ -3864,7 +3852,7 @@
         <v>19.41675838992471</v>
       </c>
       <c r="F4" t="n">
-        <v>19.41675843560638</v>
+        <v>19.41675843560637</v>
       </c>
       <c r="G4" t="n">
         <v>19.41675847585272</v>
@@ -3888,16 +3876,16 @@
         <v>19.41675866007282</v>
       </c>
       <c r="N4" t="n">
-        <v>19.4167586852156</v>
+        <v>19.41675868521559</v>
       </c>
       <c r="O4" t="n">
-        <v>19.41675870933082</v>
+        <v>19.41675870933081</v>
       </c>
       <c r="P4" t="n">
         <v>19.41675873253504</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.41675875492432</v>
+        <v>19.41675875492431</v>
       </c>
       <c r="R4" t="n">
         <v>19.41675877657891</v>
@@ -4153,7 +4141,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dr_0.0606</t>
         </is>
@@ -4165,7 +4153,7 @@
         <v>19.41675863346303</v>
       </c>
       <c r="D5" t="n">
-        <v>19.41675885665339</v>
+        <v>19.41675885665338</v>
       </c>
       <c r="E5" t="n">
         <v>19.41675902791337</v>
@@ -4460,7 +4448,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>dr_0.0808</t>
         </is>
@@ -4767,7 +4755,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>dr_0.1010</t>
         </is>
@@ -5074,7 +5062,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>dr_0.1212</t>
         </is>
@@ -5381,7 +5369,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>dr_0.1414</t>
         </is>
@@ -5564,7 +5552,7 @@
         <v>19.41680354253166</v>
       </c>
       <c r="BI9" t="n">
-        <v>19.41680393264935</v>
+        <v>19.41680393264936</v>
       </c>
       <c r="BJ9" t="n">
         <v>19.41680431947474</v>
@@ -5681,14 +5669,14 @@
         <v>19.41681686868336</v>
       </c>
       <c r="CV9" t="n">
-        <v>19.41681717086537</v>
+        <v>19.41681717086538</v>
       </c>
       <c r="CW9" t="n">
         <v>19.41681747150955</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>dr_0.1616</t>
         </is>
@@ -5995,7 +5983,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>dr_0.1818</t>
         </is>
@@ -6302,7 +6290,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>dr_0.2020</t>
         </is>
@@ -6609,7 +6597,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>dr_0.2222</t>
         </is>
@@ -6639,7 +6627,7 @@
         <v>19.41681503881922</v>
       </c>
       <c r="J13" t="n">
-        <v>19.41681897052634</v>
+        <v>19.41681897052635</v>
       </c>
       <c r="K13" t="n">
         <v>19.41682266326615</v>
@@ -6916,7 +6904,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>dr_0.2424</t>
         </is>
@@ -7223,7 +7211,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>dr_0.2626</t>
         </is>
@@ -7530,7 +7518,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>dr_0.2828</t>
         </is>
@@ -7837,7 +7825,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>dr_0.3030</t>
         </is>
@@ -8144,7 +8132,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>dr_0.3232</t>
         </is>
@@ -8451,7 +8439,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>dr_0.3434</t>
         </is>
@@ -8758,7 +8746,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>dr_0.3636</t>
         </is>
@@ -9065,7 +9053,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>dr_0.3838</t>
         </is>
@@ -9372,7 +9360,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>dr_0.4040</t>
         </is>
@@ -9679,7 +9667,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>dr_0.4242</t>
         </is>
@@ -9986,7 +9974,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>dr_0.4444</t>
         </is>
@@ -10293,7 +10281,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>dr_0.4646</t>
         </is>
@@ -10600,7 +10588,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>dr_0.4848</t>
         </is>
@@ -10907,7 +10895,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>dr_0.5051</t>
         </is>
@@ -11033,7 +11021,7 @@
         <v>19.41813955437713</v>
       </c>
       <c r="AP27" t="n">
-        <v>19.41815715306282</v>
+        <v>19.41815715306283</v>
       </c>
       <c r="AQ27" t="n">
         <v>19.41817453309999</v>
@@ -11214,7 +11202,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>dr_0.5253</t>
         </is>
@@ -11521,7 +11509,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>dr_0.5455</t>
         </is>
@@ -11828,7 +11816,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>dr_0.5657</t>
         </is>
@@ -12135,7 +12123,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>dr_0.5859</t>
         </is>
@@ -12375,7 +12363,7 @@
         <v>19.41971598355797</v>
       </c>
       <c r="CB31" t="n">
-        <v>19.41973512812115</v>
+        <v>19.41973512812114</v>
       </c>
       <c r="CC31" t="n">
         <v>19.4197541503441</v>
@@ -12429,7 +12417,7 @@
         <v>19.4200435602864</v>
       </c>
       <c r="CT31" t="n">
-        <v>19.42006080639527</v>
+        <v>19.42006080639526</v>
       </c>
       <c r="CU31" t="n">
         <v>19.42007796290646</v>
@@ -12442,7 +12430,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>dr_0.6061</t>
         </is>
@@ -12749,7 +12737,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>dr_0.6263</t>
         </is>
@@ -13056,7 +13044,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>dr_0.6465</t>
         </is>
@@ -13326,7 +13314,7 @@
         <v>19.42091552325933</v>
       </c>
       <c r="CL34" t="n">
-        <v>19.42093934730101</v>
+        <v>19.420939347301</v>
       </c>
       <c r="CM34" t="n">
         <v>19.42096303634817</v>
@@ -13363,7 +13351,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>dr_0.6667</t>
         </is>
@@ -13670,7 +13658,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>dr_0.6869</t>
         </is>
@@ -13977,7 +13965,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>dr_0.7071</t>
         </is>
@@ -14284,7 +14272,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>dr_0.7273</t>
         </is>
@@ -14371,7 +14359,7 @@
         <v>19.41993300225072</v>
       </c>
       <c r="AC38" t="n">
-        <v>19.41999348023175</v>
+        <v>19.41999348023174</v>
       </c>
       <c r="AD38" t="n">
         <v>19.42005284817356</v>
@@ -14591,7 +14579,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>dr_0.7475</t>
         </is>
@@ -14898,7 +14886,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>dr_0.7677</t>
         </is>
@@ -15078,7 +15066,7 @@
         <v>19.42223851052918</v>
       </c>
       <c r="BH40" t="n">
-        <v>19.42228637278423</v>
+        <v>19.42228637278422</v>
       </c>
       <c r="BI40" t="n">
         <v>19.4223338241381</v>
@@ -15205,7 +15193,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>dr_0.7879</t>
         </is>
@@ -15512,7 +15500,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>dr_0.8081</t>
         </is>
@@ -15819,7 +15807,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>dr_0.8283</t>
         </is>
@@ -16126,7 +16114,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>dr_0.8485</t>
         </is>
@@ -16243,7 +16231,7 @@
         <v>19.42254418661452</v>
       </c>
       <c r="AM44" t="n">
-        <v>19.42262399404182</v>
+        <v>19.42262399404181</v>
       </c>
       <c r="AN44" t="n">
         <v>19.42270272996248</v>
@@ -16336,7 +16324,7 @@
         <v>19.42465146845493</v>
       </c>
       <c r="BR44" t="n">
-        <v>19.42471015156321</v>
+        <v>19.4247101515632</v>
       </c>
       <c r="BS44" t="n">
         <v>19.42476840467564</v>
@@ -16433,7 +16421,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>dr_0.8687</t>
         </is>
@@ -16691,7 +16679,7 @@
         <v>19.42615015537455</v>
       </c>
       <c r="CH45" t="n">
-        <v>19.42620655952256</v>
+        <v>19.42620655952255</v>
       </c>
       <c r="CI45" t="n">
         <v>19.42626262885823</v>
@@ -16740,7 +16728,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>dr_0.8889</t>
         </is>
@@ -17047,7 +17035,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>dr_0.9091</t>
         </is>
@@ -17314,7 +17302,7 @@
         <v>19.42763486975637</v>
       </c>
       <c r="CK47" t="n">
-        <v>19.42769791741083</v>
+        <v>19.42769791741082</v>
       </c>
       <c r="CL47" t="n">
         <v>19.42776060367584</v>
@@ -17354,7 +17342,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>dr_0.9293</t>
         </is>
@@ -17661,7 +17649,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>dr_0.9495</t>
         </is>
@@ -17968,7 +17956,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>dr_0.9697</t>
         </is>
@@ -17998,7 +17986,7 @@
         <v>19.42048525179865</v>
       </c>
       <c r="J50" t="n">
-        <v>19.42074258337091</v>
+        <v>19.42074258337092</v>
       </c>
       <c r="K50" t="n">
         <v>19.42098427330617</v>
@@ -18275,7 +18263,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>dr_0.9899</t>
         </is>
@@ -18582,7 +18570,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>dr_1.0101</t>
         </is>
@@ -18807,7 +18795,7 @@
         <v>19.43017863847594</v>
       </c>
       <c r="BW52" t="n">
-        <v>19.4302715032338</v>
+        <v>19.43027150323379</v>
       </c>
       <c r="BX52" t="n">
         <v>19.43036373391586</v>
@@ -18889,7 +18877,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>dr_1.0303</t>
         </is>
@@ -19196,7 +19184,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>dr_1.0505</t>
         </is>
@@ -19503,7 +19491,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>dr_1.0707</t>
         </is>
@@ -19810,7 +19798,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>dr_1.0909</t>
         </is>
@@ -20117,7 +20105,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>dr_1.1111</t>
         </is>
@@ -20129,7 +20117,7 @@
         <v>19.41883122792596</v>
       </c>
       <c r="D57" t="n">
-        <v>19.41968992360954</v>
+        <v>19.41968992360953</v>
       </c>
       <c r="E57" t="n">
         <v>19.4203488143531</v>
@@ -20153,7 +20141,7 @@
         <v>19.42297724620689</v>
       </c>
       <c r="L57" t="n">
-        <v>19.42331363475916</v>
+        <v>19.42331363475915</v>
       </c>
       <c r="M57" t="n">
         <v>19.42363358193762</v>
@@ -20424,7 +20412,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>dr_1.1313</t>
         </is>
@@ -20673,7 +20661,7 @@
         <v>19.43627038459014</v>
       </c>
       <c r="CE58" t="n">
-        <v>19.43639193467951</v>
+        <v>19.4363919346795</v>
       </c>
       <c r="CF58" t="n">
         <v>19.436512736465</v>
@@ -20731,7 +20719,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>dr_1.1515</t>
         </is>
@@ -21031,14 +21019,14 @@
         <v>19.43934996015811</v>
       </c>
       <c r="CV59" t="n">
-        <v>19.43946608907247</v>
+        <v>19.43946608907248</v>
       </c>
       <c r="CW59" t="n">
         <v>19.43958162673064</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>dr_1.1717</t>
         </is>
@@ -21345,7 +21333,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>dr_1.1919</t>
         </is>
@@ -21652,7 +21640,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>dr_1.2121</t>
         </is>
@@ -21959,7 +21947,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>dr_1.2323</t>
         </is>
@@ -22266,7 +22254,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>dr_1.2525</t>
         </is>
@@ -22573,7 +22561,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>dr_1.2727</t>
         </is>
@@ -22880,7 +22868,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>dr_1.2929</t>
         </is>
@@ -23187,7 +23175,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>dr_1.3131</t>
         </is>
@@ -23494,7 +23482,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>dr_1.3333</t>
         </is>
@@ -23801,7 +23789,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>dr_1.3535</t>
         </is>
@@ -23843,7 +23831,7 @@
         <v>19.42879569816155</v>
       </c>
       <c r="N69" t="n">
-        <v>19.42933089666023</v>
+        <v>19.42933089666022</v>
       </c>
       <c r="O69" t="n">
         <v>19.42984421718672</v>
@@ -24108,7 +24096,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>dr_1.3737</t>
         </is>
@@ -24415,7 +24403,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>dr_1.3939</t>
         </is>
@@ -24722,7 +24710,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>dr_1.4141</t>
         </is>
@@ -24836,7 +24824,7 @@
         <v>19.44106982715396</v>
       </c>
       <c r="AL72" t="n">
-        <v>19.44141460975885</v>
+        <v>19.44141460975884</v>
       </c>
       <c r="AM72" t="n">
         <v>19.44175463381488</v>
@@ -25029,7 +25017,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>dr_1.4343</t>
         </is>
@@ -25336,7 +25324,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>dr_1.4545</t>
         </is>
@@ -25643,7 +25631,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>dr_1.4747</t>
         </is>
@@ -25950,7 +25938,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>dr_1.4949</t>
         </is>
@@ -26257,7 +26245,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>dr_1.5152</t>
         </is>
@@ -26461,7 +26449,7 @@
         <v>19.45704926096909</v>
       </c>
       <c r="BP77" t="n">
-        <v>19.45735788932114</v>
+        <v>19.45735788932113</v>
       </c>
       <c r="BQ77" t="n">
         <v>19.45766418648766</v>
@@ -26564,7 +26552,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>dr_1.5354</t>
         </is>
@@ -26871,7 +26859,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>dr_1.5556</t>
         </is>
@@ -27178,7 +27166,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>dr_1.5758</t>
         </is>
@@ -27485,7 +27473,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>dr_1.5960</t>
         </is>
@@ -27500,7 +27488,7 @@
         <v>19.42495115483104</v>
       </c>
       <c r="E81" t="n">
-        <v>19.42679232517004</v>
+        <v>19.42679232517003</v>
       </c>
       <c r="F81" t="n">
         <v>19.42834445284111</v>
@@ -27792,7 +27780,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>dr_1.6162</t>
         </is>
@@ -28099,7 +28087,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>dr_1.6364</t>
         </is>
@@ -28198,7 +28186,7 @@
         <v>19.45081453777541</v>
       </c>
       <c r="AG83" t="n">
-        <v>19.45137730462695</v>
+        <v>19.45137730462694</v>
       </c>
       <c r="AH83" t="n">
         <v>19.45193105950784</v>
@@ -28406,7 +28394,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>dr_1.6566</t>
         </is>
@@ -28713,7 +28701,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>dr_1.6768</t>
         </is>
@@ -29020,7 +29008,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>dr_1.6970</t>
         </is>
@@ -29077,7 +29065,7 @@
         <v>19.44433536080204</v>
       </c>
       <c r="S86" t="n">
-        <v>19.44518385760356</v>
+        <v>19.44518385760355</v>
       </c>
       <c r="T86" t="n">
         <v>19.44600773127044</v>
@@ -29327,7 +29315,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>dr_1.7172</t>
         </is>
@@ -29549,7 +29537,7 @@
         <v>19.47681614031206</v>
       </c>
       <c r="BV87" t="n">
-        <v>19.47723735991444</v>
+        <v>19.47723735991443</v>
       </c>
       <c r="BW87" t="n">
         <v>19.47765566101177</v>
@@ -29634,7 +29622,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>dr_1.7374</t>
         </is>
@@ -29941,7 +29929,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>dr_1.7576</t>
         </is>
@@ -30248,7 +30236,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>dr_1.7778</t>
         </is>
@@ -30555,7 +30543,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>dr_1.7980</t>
         </is>
@@ -30862,7 +30850,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>dr_1.8182</t>
         </is>
@@ -31169,7 +31157,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>dr_1.8384</t>
         </is>
@@ -31476,7 +31464,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>dr_1.8586</t>
         </is>
@@ -31783,7 +31771,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>dr_1.8788</t>
         </is>
@@ -32002,7 +31990,7 @@
         <v>19.49372202322102</v>
       </c>
       <c r="BU95" t="n">
-        <v>19.49426940704968</v>
+        <v>19.49426940704967</v>
       </c>
       <c r="BV95" t="n">
         <v>19.49481294372777</v>
@@ -32090,7 +32078,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>dr_1.8990</t>
         </is>
@@ -32105,7 +32093,7 @@
         <v>19.43017652646536</v>
       </c>
       <c r="E96" t="n">
-        <v>19.43319177294654</v>
+        <v>19.43319177294655</v>
       </c>
       <c r="F96" t="n">
         <v>19.43573360725809</v>
@@ -32397,7 +32385,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>dr_1.9192</t>
         </is>
@@ -32688,7 +32676,7 @@
         <v>19.51148067595853</v>
       </c>
       <c r="CS97" t="n">
-        <v>19.51198272550387</v>
+        <v>19.51198272550388</v>
       </c>
       <c r="CT97" t="n">
         <v>19.51248213473921</v>
@@ -32704,7 +32692,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>dr_1.9394</t>
         </is>
@@ -33011,7 +32999,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>dr_1.9596</t>
         </is>
@@ -33318,7 +33306,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>dr_1.9798</t>
         </is>
@@ -33625,7 +33613,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>dr_2.0000</t>
         </is>
@@ -33946,42 +33934,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>equation</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>drug</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>R0_O2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Emax_O2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kappa_O2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tau_O2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>n_O2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>m_O2</t>
         </is>
@@ -34032,27 +34020,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Heatmap_Source</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Coefficient_Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -34061,12 +34049,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\Heatmaps\Nifedipine\O2_mean_sorted.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/Heatmaps/Nifedipine/O2_mean_sorted.csv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\EQN_Coefficients\all_equations_coefficients.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/EQN_Coefficients/all_equations_coefficients.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
